--- a/data/Data.xlsx
+++ b/data/Data.xlsx
@@ -1059,7 +1059,7 @@
   <cols>
     <col min="1" max="1" width="17.6388888888889" customWidth="1"/>
     <col min="2" max="2" width="9.13888888888889" customWidth="1"/>
-    <col min="3" max="3" width="56.6388888888889" customWidth="1"/>
+    <col min="3" max="3" width="115.555555555556" customWidth="1"/>
     <col min="5" max="5" width="27.5185185185185" customWidth="1"/>
     <col min="6" max="6" width="32.287037037037" customWidth="1"/>
   </cols>
